--- a/data/ams_weekly_data/White_Mulberry/business_report_week26.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,25 +548,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79476</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>WM-LOD-WH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WM-LOD-WH</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
@@ -598,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -625,25 +629,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79477</t>
+          <t>FBA76418</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>WM-LOD-IN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WM-LOD-IN</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
@@ -675,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -702,25 +710,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79478</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>WM-LOD-BK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WM-LOD-BK</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
@@ -752,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -779,25 +791,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>WM-LOD-CF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WM-LOD-CF</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
@@ -829,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -856,25 +872,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79613</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM-GD07-CB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WM-GD07-CB</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
@@ -906,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -933,25 +953,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>WM-SE08-CF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WM-SE08-CF</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -983,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1010,77 +1034,1539 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>FBA79476</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79477</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WM-GS2M-BK</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WM-GS2M-BK</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FBA79478</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FBA79479</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBA79613</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MS1ML</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MS1ML</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FBA79612</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WM1ML</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WM1ML</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBA79615</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VLMS1ML</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VLMS1ML</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBA79614</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MS2ML</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DP313R77</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>B0DP313R77</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MS2ML</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FBA79616</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HD1ML</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HD1ML</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>FBA79617</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>HDWF1ML</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>B0DP32F346</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>B0DP32F346</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>12</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FBA79662</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-MODL-WH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WM-MODL-WH</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FBA79790</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TVLF1ML</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TVLF1ML</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FBK79788</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TVCT1ML</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TVCT1ML</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FBK79789</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TVMF1ML</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TVMF1ML</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FBK79784</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>POS2M</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>POS2M</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FBK79786</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>POSS-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>POSS-01</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FBK79787</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TVCF1ML</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TVCF1ML</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FBK79791</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TVFM1ML</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TVFM1ML</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FBK79792</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HDMSP1ML</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HDMSP1ML</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week26.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week26.xlsx
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1586</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>49527.97</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>14150.85</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1662</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>43215.25</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6575</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>9020</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>255055.08</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1366</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1828</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>25425.42</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1676</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2228</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>9786.440000000001</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3861.86</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>820</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>959</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1292</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>46883.9</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>739</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>17791.53</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4744.07</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>948</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>63436.43</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2471.19</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3999.15</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>25515.25</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>9320.34</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>15246.61</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1235.59</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1778.81</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>9879.66</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week26.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week26.xlsx
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>9786.440000000001</v>
+        <v>68027.94</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3861.86</v>
+        <v>11148.3</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>11606.78</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>16940.63</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>46883.9</v>
+        <v>80765.25</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>17791.53</v>
+        <v>23340.68</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>31515.3</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
